--- a/office/file/25机械12考勤表.xlsx
+++ b/office/file/25机械12考勤表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{32744E79-5F4A-4C4F-9D0A-F4549B7E4597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{8CCFD81E-1C5C-418F-BC76-6D29782E94E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8CCFD81E-1C5C-418F-BC76-6D29782E94E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1242,15 +1242,33 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1269,25 +1287,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1655,250 +1655,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="7"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="13"/>
     </row>
     <row r="2" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="10"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="16"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="15" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="15" t="s">
+      <c r="L3" s="6"/>
+      <c r="M3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="15" t="s">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="15" t="s">
+      <c r="R3" s="6"/>
+      <c r="S3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="6"/>
+      <c r="U3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="15" t="s">
+      <c r="V3" s="6"/>
+      <c r="W3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="15" t="s">
+      <c r="X3" s="6"/>
+      <c r="Y3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="15" t="s">
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="15" t="s">
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="15" t="s">
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="15" t="s">
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="15" t="s">
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="15" t="s">
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="16"/>
-      <c r="AM3" s="11" t="s">
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15" t="s">
+      <c r="L4" s="6"/>
+      <c r="M4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="15" t="s">
+      <c r="N4" s="6"/>
+      <c r="O4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="15" t="s">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="14"/>
-      <c r="S4" s="15" t="s">
+      <c r="R4" s="6"/>
+      <c r="S4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T4" s="14"/>
-      <c r="U4" s="15" t="s">
+      <c r="T4" s="6"/>
+      <c r="U4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="14"/>
-      <c r="W4" s="15" t="s">
+      <c r="V4" s="6"/>
+      <c r="W4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="15" t="s">
+      <c r="X4" s="6"/>
+      <c r="Y4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="15" t="s">
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="15" t="s">
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="15" t="s">
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="15" t="s">
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH4" s="14"/>
-      <c r="AI4" s="15" t="s">
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="15" t="s">
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="17"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="9"/>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
@@ -3116,250 +3116,250 @@
       <c r="AM31" s="2"/>
     </row>
     <row r="32" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="6"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="6"/>
-      <c r="AJ32" s="6"/>
-      <c r="AK32" s="6"/>
-      <c r="AL32" s="6"/>
-      <c r="AM32" s="7"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="12"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="12"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
+      <c r="AI32" s="12"/>
+      <c r="AJ32" s="12"/>
+      <c r="AK32" s="12"/>
+      <c r="AL32" s="12"/>
+      <c r="AM32" s="13"/>
     </row>
     <row r="33" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="9"/>
-      <c r="AE33" s="9"/>
-      <c r="AF33" s="9"/>
-      <c r="AG33" s="9"/>
-      <c r="AH33" s="9"/>
-      <c r="AI33" s="9"/>
-      <c r="AJ33" s="9"/>
-      <c r="AK33" s="9"/>
-      <c r="AL33" s="9"/>
-      <c r="AM33" s="10"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="16"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="s">
+      <c r="H34" s="6"/>
+      <c r="I34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="15" t="s">
+      <c r="J34" s="6"/>
+      <c r="K34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="15" t="s">
+      <c r="L34" s="6"/>
+      <c r="M34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="15" t="s">
+      <c r="N34" s="6"/>
+      <c r="O34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="15" t="s">
+      <c r="P34" s="6"/>
+      <c r="Q34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R34" s="14"/>
-      <c r="S34" s="15" t="s">
+      <c r="R34" s="6"/>
+      <c r="S34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="14"/>
-      <c r="U34" s="15" t="s">
+      <c r="T34" s="6"/>
+      <c r="U34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="V34" s="14"/>
-      <c r="W34" s="15" t="s">
+      <c r="V34" s="6"/>
+      <c r="W34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="15" t="s">
+      <c r="X34" s="6"/>
+      <c r="Y34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="15" t="s">
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="15" t="s">
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="15" t="s">
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AF34" s="14"/>
-      <c r="AG34" s="15" t="s">
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AH34" s="14"/>
-      <c r="AI34" s="15" t="s">
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ34" s="14"/>
-      <c r="AK34" s="15" t="s">
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="11" t="s">
+      <c r="AL34" s="7"/>
+      <c r="AM34" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15" t="s">
+      <c r="D35" s="6"/>
+      <c r="E35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="15" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="s">
+      <c r="H35" s="6"/>
+      <c r="I35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="15" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="15" t="s">
+      <c r="L35" s="6"/>
+      <c r="M35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15" t="s">
+      <c r="N35" s="6"/>
+      <c r="O35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="15" t="s">
+      <c r="P35" s="6"/>
+      <c r="Q35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R35" s="14"/>
-      <c r="S35" s="15" t="s">
+      <c r="R35" s="6"/>
+      <c r="S35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T35" s="14"/>
-      <c r="U35" s="15" t="s">
+      <c r="T35" s="6"/>
+      <c r="U35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V35" s="14"/>
-      <c r="W35" s="15" t="s">
+      <c r="V35" s="6"/>
+      <c r="W35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="15" t="s">
+      <c r="X35" s="6"/>
+      <c r="Y35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="15" t="s">
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="15" t="s">
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="15" t="s">
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF35" s="14"/>
-      <c r="AG35" s="15" t="s">
+      <c r="AF35" s="6"/>
+      <c r="AG35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH35" s="14"/>
-      <c r="AI35" s="15" t="s">
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ35" s="14"/>
-      <c r="AK35" s="15" t="s">
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="17"/>
+      <c r="AL35" s="7"/>
+      <c r="AM35" s="9"/>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -4577,250 +4577,250 @@
       <c r="AM62" s="2"/>
     </row>
     <row r="63" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
-      <c r="Y63" s="6"/>
-      <c r="Z63" s="6"/>
-      <c r="AA63" s="6"/>
-      <c r="AB63" s="6"/>
-      <c r="AC63" s="6"/>
-      <c r="AD63" s="6"/>
-      <c r="AE63" s="6"/>
-      <c r="AF63" s="6"/>
-      <c r="AG63" s="6"/>
-      <c r="AH63" s="6"/>
-      <c r="AI63" s="6"/>
-      <c r="AJ63" s="6"/>
-      <c r="AK63" s="6"/>
-      <c r="AL63" s="6"/>
-      <c r="AM63" s="7"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="12"/>
+      <c r="S63" s="12"/>
+      <c r="T63" s="12"/>
+      <c r="U63" s="12"/>
+      <c r="V63" s="12"/>
+      <c r="W63" s="12"/>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="12"/>
+      <c r="Z63" s="12"/>
+      <c r="AA63" s="12"/>
+      <c r="AB63" s="12"/>
+      <c r="AC63" s="12"/>
+      <c r="AD63" s="12"/>
+      <c r="AE63" s="12"/>
+      <c r="AF63" s="12"/>
+      <c r="AG63" s="12"/>
+      <c r="AH63" s="12"/>
+      <c r="AI63" s="12"/>
+      <c r="AJ63" s="12"/>
+      <c r="AK63" s="12"/>
+      <c r="AL63" s="12"/>
+      <c r="AM63" s="13"/>
     </row>
     <row r="64" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
-      <c r="Q64" s="9"/>
-      <c r="R64" s="9"/>
-      <c r="S64" s="9"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="9"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
-      <c r="AA64" s="9"/>
-      <c r="AB64" s="9"/>
-      <c r="AC64" s="9"/>
-      <c r="AD64" s="9"/>
-      <c r="AE64" s="9"/>
-      <c r="AF64" s="9"/>
-      <c r="AG64" s="9"/>
-      <c r="AH64" s="9"/>
-      <c r="AI64" s="9"/>
-      <c r="AJ64" s="9"/>
-      <c r="AK64" s="9"/>
-      <c r="AL64" s="9"/>
-      <c r="AM64" s="10"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="15"/>
+      <c r="S64" s="15"/>
+      <c r="T64" s="15"/>
+      <c r="U64" s="15"/>
+      <c r="V64" s="15"/>
+      <c r="W64" s="15"/>
+      <c r="X64" s="15"/>
+      <c r="Y64" s="15"/>
+      <c r="Z64" s="15"/>
+      <c r="AA64" s="15"/>
+      <c r="AB64" s="15"/>
+      <c r="AC64" s="15"/>
+      <c r="AD64" s="15"/>
+      <c r="AE64" s="15"/>
+      <c r="AF64" s="15"/>
+      <c r="AG64" s="15"/>
+      <c r="AH64" s="15"/>
+      <c r="AI64" s="15"/>
+      <c r="AJ64" s="15"/>
+      <c r="AK64" s="15"/>
+      <c r="AL64" s="15"/>
+      <c r="AM64" s="16"/>
     </row>
     <row r="65" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="15" t="s">
+      <c r="D65" s="6"/>
+      <c r="E65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="15" t="s">
+      <c r="F65" s="6"/>
+      <c r="G65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="s">
+      <c r="H65" s="6"/>
+      <c r="I65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J65" s="14"/>
-      <c r="K65" s="15" t="s">
+      <c r="J65" s="6"/>
+      <c r="K65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L65" s="14"/>
-      <c r="M65" s="15" t="s">
+      <c r="L65" s="6"/>
+      <c r="M65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N65" s="14"/>
-      <c r="O65" s="15" t="s">
+      <c r="N65" s="6"/>
+      <c r="O65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="15" t="s">
+      <c r="P65" s="6"/>
+      <c r="Q65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R65" s="14"/>
-      <c r="S65" s="15" t="s">
+      <c r="R65" s="6"/>
+      <c r="S65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T65" s="14"/>
-      <c r="U65" s="15" t="s">
+      <c r="T65" s="6"/>
+      <c r="U65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="V65" s="14"/>
-      <c r="W65" s="15" t="s">
+      <c r="V65" s="6"/>
+      <c r="W65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X65" s="14"/>
-      <c r="Y65" s="15" t="s">
+      <c r="X65" s="6"/>
+      <c r="Y65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Z65" s="14"/>
-      <c r="AA65" s="15" t="s">
+      <c r="Z65" s="6"/>
+      <c r="AA65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AB65" s="14"/>
-      <c r="AC65" s="15" t="s">
+      <c r="AB65" s="6"/>
+      <c r="AC65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AD65" s="14"/>
-      <c r="AE65" s="15" t="s">
+      <c r="AD65" s="6"/>
+      <c r="AE65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AF65" s="14"/>
-      <c r="AG65" s="15" t="s">
+      <c r="AF65" s="6"/>
+      <c r="AG65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AH65" s="14"/>
-      <c r="AI65" s="15" t="s">
+      <c r="AH65" s="6"/>
+      <c r="AI65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ65" s="14"/>
-      <c r="AK65" s="15" t="s">
+      <c r="AJ65" s="6"/>
+      <c r="AK65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AL65" s="16"/>
-      <c r="AM65" s="11" t="s">
+      <c r="AL65" s="7"/>
+      <c r="AM65" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="15" t="s">
+      <c r="D66" s="6"/>
+      <c r="E66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="15" t="s">
+      <c r="F66" s="6"/>
+      <c r="G66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="s">
+      <c r="H66" s="6"/>
+      <c r="I66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J66" s="14"/>
-      <c r="K66" s="15" t="s">
+      <c r="J66" s="6"/>
+      <c r="K66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L66" s="14"/>
-      <c r="M66" s="15" t="s">
+      <c r="L66" s="6"/>
+      <c r="M66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N66" s="14"/>
-      <c r="O66" s="15" t="s">
+      <c r="N66" s="6"/>
+      <c r="O66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="15" t="s">
+      <c r="P66" s="6"/>
+      <c r="Q66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R66" s="14"/>
-      <c r="S66" s="15" t="s">
+      <c r="R66" s="6"/>
+      <c r="S66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T66" s="14"/>
-      <c r="U66" s="15" t="s">
+      <c r="T66" s="6"/>
+      <c r="U66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V66" s="14"/>
-      <c r="W66" s="15" t="s">
+      <c r="V66" s="6"/>
+      <c r="W66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X66" s="14"/>
-      <c r="Y66" s="15" t="s">
+      <c r="X66" s="6"/>
+      <c r="Y66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Z66" s="14"/>
-      <c r="AA66" s="15" t="s">
+      <c r="Z66" s="6"/>
+      <c r="AA66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB66" s="14"/>
-      <c r="AC66" s="15" t="s">
+      <c r="AB66" s="6"/>
+      <c r="AC66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD66" s="14"/>
-      <c r="AE66" s="15" t="s">
+      <c r="AD66" s="6"/>
+      <c r="AE66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF66" s="14"/>
-      <c r="AG66" s="15" t="s">
+      <c r="AF66" s="6"/>
+      <c r="AG66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH66" s="14"/>
-      <c r="AI66" s="15" t="s">
+      <c r="AH66" s="6"/>
+      <c r="AI66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ66" s="14"/>
-      <c r="AK66" s="15" t="s">
+      <c r="AJ66" s="6"/>
+      <c r="AK66" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AL66" s="16"/>
-      <c r="AM66" s="17"/>
+      <c r="AL66" s="7"/>
+      <c r="AM66" s="9"/>
     </row>
     <row r="67" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
@@ -6318,81 +6318,30 @@
     </row>
   </sheetData>
   <mergeCells count="123">
-    <mergeCell ref="AG66:AH66"/>
-    <mergeCell ref="AI66:AJ66"/>
-    <mergeCell ref="AK66:AL66"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="W66:X66"/>
-    <mergeCell ref="Y66:Z66"/>
-    <mergeCell ref="AA66:AB66"/>
-    <mergeCell ref="AC66:AD66"/>
-    <mergeCell ref="AE66:AF66"/>
-    <mergeCell ref="AM65:AM66"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="O66:P66"/>
-    <mergeCell ref="Q66:R66"/>
-    <mergeCell ref="S66:T66"/>
-    <mergeCell ref="AA65:AB65"/>
-    <mergeCell ref="AC65:AD65"/>
-    <mergeCell ref="AE65:AF65"/>
-    <mergeCell ref="AG65:AH65"/>
-    <mergeCell ref="AI65:AJ65"/>
-    <mergeCell ref="AK65:AL65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="Q65:R65"/>
-    <mergeCell ref="S65:T65"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="W65:X65"/>
-    <mergeCell ref="Y65:Z65"/>
-    <mergeCell ref="A63:AM63"/>
-    <mergeCell ref="A64:AM64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="AA35:AB35"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="Y35:Z35"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AI34:AJ34"/>
-    <mergeCell ref="AK34:AL34"/>
-    <mergeCell ref="AM34:AM35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Y34:Z34"/>
-    <mergeCell ref="AA34:AB34"/>
-    <mergeCell ref="AC34:AD34"/>
-    <mergeCell ref="AE34:AF34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="A1:AM1"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="AG4:AH4"/>
     <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="AK4:AL4"/>
@@ -6417,34 +6366,85 @@
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="A1:AM1"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AI34:AJ34"/>
+    <mergeCell ref="AK34:AL34"/>
+    <mergeCell ref="AM34:AM35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Y34:Z34"/>
+    <mergeCell ref="AA34:AB34"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="AA35:AB35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="Y35:Z35"/>
+    <mergeCell ref="A63:AM63"/>
+    <mergeCell ref="A64:AM64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="AM65:AM66"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="Q66:R66"/>
+    <mergeCell ref="S66:T66"/>
+    <mergeCell ref="AA65:AB65"/>
+    <mergeCell ref="AC65:AD65"/>
+    <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="AG65:AH65"/>
+    <mergeCell ref="AI65:AJ65"/>
+    <mergeCell ref="AK65:AL65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="S65:T65"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="W65:X65"/>
+    <mergeCell ref="Y65:Z65"/>
+    <mergeCell ref="AG66:AH66"/>
+    <mergeCell ref="AI66:AJ66"/>
+    <mergeCell ref="AK66:AL66"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="W66:X66"/>
+    <mergeCell ref="Y66:Z66"/>
+    <mergeCell ref="AA66:AB66"/>
+    <mergeCell ref="AC66:AD66"/>
+    <mergeCell ref="AE66:AF66"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.38" right="0.33" top="0.62" bottom="0.73" header="0.4" footer="0.35"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;R&amp;10教师签字:__________________                         系(教研室主任签字):__________________       </oddFooter>
   </headerFooter>
@@ -6454,7 +6454,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA65D70-568D-463F-9DA0-E3A930CA95E7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6464,7 +6464,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B04FBD9-3137-48D9-A20A-E902764DF972}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
